--- a/Entrega_6/fuerzas_por_columna.xlsx
+++ b/Entrega_6/fuerzas_por_columna.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e453337d7bb58d0d/Escritorio/Semestre XI/Proyecto Civil/Proyecto_civil/Entrega_6/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_FFC65FC089212DEEF11F73EBE1F3DE57538CDF63" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F73BBDC-A82B-45A0-9135-96A3A9445689}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="9810" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -181,8 +187,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,13 +225,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -263,7 +277,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -297,6 +311,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -331,9 +346,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,12 +521,34 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3119767C-D664-45C8-A371-FF5F65570D30}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;58c1b6de-1a64-4a63-9b3e-1d2b0532358b&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AS10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -647,7 +685,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -655,7 +693,7 @@
         <v>9.891</v>
       </c>
       <c r="C2">
-        <v>47.709</v>
+        <v>47.709000000000003</v>
       </c>
       <c r="D2">
         <v>0.3</v>
@@ -667,31 +705,31 @@
         <v>-20.0289</v>
       </c>
       <c r="G2">
-        <v>-21.0039</v>
+        <v>-21.003900000000002</v>
       </c>
       <c r="H2">
-        <v>0.2201</v>
+        <v>0.22009999999999999</v>
       </c>
       <c r="I2">
-        <v>0.2201</v>
+        <v>0.22009999999999999</v>
       </c>
       <c r="J2">
-        <v>-0.0025</v>
+        <v>-2.5000000000000001E-3</v>
       </c>
       <c r="K2">
-        <v>-0.0025</v>
+        <v>-2.5000000000000001E-3</v>
       </c>
       <c r="L2">
-        <v>-0.007</v>
+        <v>-7.0000000000000001E-3</v>
       </c>
       <c r="M2">
-        <v>-0.0134</v>
+        <v>-1.34E-2</v>
       </c>
       <c r="N2">
         <v>0.1512</v>
       </c>
       <c r="O2">
-        <v>-0.421</v>
+        <v>-0.42099999999999999</v>
       </c>
       <c r="P2">
         <v>-17.1816</v>
@@ -706,52 +744,52 @@
         <v>0.2006</v>
       </c>
       <c r="T2">
-        <v>-0.0054</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="U2">
-        <v>-0.0054</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="V2">
-        <v>-0.0021</v>
+        <v>-2.0999999999999999E-3</v>
       </c>
       <c r="W2">
-        <v>-0.0162</v>
+        <v>-1.6199999999999999E-2</v>
       </c>
       <c r="X2">
-        <v>0.1354</v>
+        <v>0.13539999999999999</v>
       </c>
       <c r="Y2">
-        <v>-0.3862</v>
+        <v>-0.38619999999999999</v>
       </c>
       <c r="Z2">
-        <v>0.0693</v>
+        <v>6.93E-2</v>
       </c>
       <c r="AA2">
-        <v>0.0693</v>
+        <v>6.93E-2</v>
       </c>
       <c r="AB2">
-        <v>0.2966</v>
+        <v>0.29659999999999997</v>
       </c>
       <c r="AC2">
-        <v>0.2966</v>
+        <v>0.29659999999999997</v>
       </c>
       <c r="AD2">
-        <v>0.0583</v>
+        <v>5.8299999999999998E-2</v>
       </c>
       <c r="AE2">
-        <v>0.0583</v>
+        <v>5.8299999999999998E-2</v>
       </c>
       <c r="AF2">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="AG2">
-        <v>0.0057</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="AH2">
-        <v>0.4393</v>
+        <v>0.43930000000000002</v>
       </c>
       <c r="AI2">
-        <v>0.0544</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="AJ2">
         <v>0.1076</v>
@@ -760,31 +798,31 @@
         <v>0.1076</v>
       </c>
       <c r="AL2">
-        <v>0.0759</v>
+        <v>7.5899999999999995E-2</v>
       </c>
       <c r="AM2">
-        <v>0.0759</v>
+        <v>7.5899999999999995E-2</v>
       </c>
       <c r="AN2">
-        <v>0.1436</v>
+        <v>0.14360000000000001</v>
       </c>
       <c r="AO2">
-        <v>0.1436</v>
+        <v>0.14360000000000001</v>
       </c>
       <c r="AP2">
-        <v>0.1952</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="AQ2">
-        <v>0.008699999999999999</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="AR2">
-        <v>0.1214</v>
+        <v>0.12139999999999999</v>
       </c>
       <c r="AS2">
-        <v>0.0374</v>
+        <v>3.7400000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:45">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -792,7 +830,7 @@
         <v>9.891</v>
       </c>
       <c r="C3">
-        <v>42.109</v>
+        <v>42.109000000000002</v>
       </c>
       <c r="D3">
         <v>0.3</v>
@@ -801,52 +839,52 @@
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>-19.4705</v>
+        <v>-19.470500000000001</v>
       </c>
       <c r="G3">
-        <v>-20.4455</v>
+        <v>-20.445499999999999</v>
       </c>
       <c r="H3">
-        <v>0.6881</v>
+        <v>0.68810000000000004</v>
       </c>
       <c r="I3">
-        <v>0.6881</v>
+        <v>0.68810000000000004</v>
       </c>
       <c r="J3">
-        <v>-0.2211</v>
+        <v>-0.22109999999999999</v>
       </c>
       <c r="K3">
-        <v>-0.2211</v>
+        <v>-0.22109999999999999</v>
       </c>
       <c r="L3">
-        <v>0.3756</v>
+        <v>0.37559999999999999</v>
       </c>
       <c r="M3">
-        <v>-0.1992</v>
+        <v>-0.19919999999999999</v>
       </c>
       <c r="N3">
-        <v>0.5385</v>
+        <v>0.53849999999999998</v>
       </c>
       <c r="O3">
-        <v>-1.2506</v>
+        <v>-1.2505999999999999</v>
       </c>
       <c r="P3">
-        <v>-16.7007</v>
+        <v>-16.700700000000001</v>
       </c>
       <c r="Q3">
-        <v>-16.7007</v>
+        <v>-16.700700000000001</v>
       </c>
       <c r="R3">
-        <v>0.6427</v>
+        <v>0.64270000000000005</v>
       </c>
       <c r="S3">
-        <v>0.6427</v>
+        <v>0.64270000000000005</v>
       </c>
       <c r="T3">
-        <v>-0.2025</v>
+        <v>-0.20250000000000001</v>
       </c>
       <c r="U3">
-        <v>-0.2025</v>
+        <v>-0.20250000000000001</v>
       </c>
       <c r="V3">
         <v>0.3427</v>
@@ -855,7 +893,7 @@
         <v>-0.1837</v>
       </c>
       <c r="X3">
-        <v>0.5037</v>
+        <v>0.50370000000000004</v>
       </c>
       <c r="Y3">
         <v>-1.1673</v>
@@ -867,34 +905,34 @@
         <v>0.1062</v>
       </c>
       <c r="AB3">
-        <v>0.3364</v>
+        <v>0.33639999999999998</v>
       </c>
       <c r="AC3">
-        <v>0.3364</v>
+        <v>0.33639999999999998</v>
       </c>
       <c r="AD3">
-        <v>0.0327</v>
+        <v>3.27E-2</v>
       </c>
       <c r="AE3">
-        <v>0.0327</v>
+        <v>3.27E-2</v>
       </c>
       <c r="AF3">
-        <v>0.052</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="AG3">
-        <v>0.009900000000000001</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="AH3">
-        <v>0.4986</v>
+        <v>0.49859999999999999</v>
       </c>
       <c r="AI3">
-        <v>0.063</v>
+        <v>6.3E-2</v>
       </c>
       <c r="AJ3">
-        <v>0.2227</v>
+        <v>0.22270000000000001</v>
       </c>
       <c r="AK3">
-        <v>0.2227</v>
+        <v>0.22270000000000001</v>
       </c>
       <c r="AL3">
         <v>0.113</v>
@@ -909,19 +947,19 @@
         <v>0.1198</v>
       </c>
       <c r="AP3">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="AQ3">
-        <v>0.0194</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="AR3">
         <v>0.188</v>
       </c>
       <c r="AS3">
-        <v>0.053</v>
+        <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:45">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -929,7 +967,7 @@
         <v>9.891</v>
       </c>
       <c r="C4">
-        <v>37.109</v>
+        <v>37.109000000000002</v>
       </c>
       <c r="D4">
         <v>0.3</v>
@@ -938,10 +976,10 @@
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>-19.3311</v>
+        <v>-19.331099999999999</v>
       </c>
       <c r="G4">
-        <v>-20.3061</v>
+        <v>-20.306100000000001</v>
       </c>
       <c r="H4">
         <v>1.0402</v>
@@ -956,16 +994,16 @@
         <v>0.122</v>
       </c>
       <c r="L4">
-        <v>0.0924</v>
+        <v>9.2399999999999996E-2</v>
       </c>
       <c r="M4">
         <v>-0.2248</v>
       </c>
       <c r="N4">
-        <v>0.8303</v>
+        <v>0.83030000000000004</v>
       </c>
       <c r="O4">
-        <v>-1.8743</v>
+        <v>-1.8743000000000001</v>
       </c>
       <c r="P4">
         <v>-16.4557</v>
@@ -974,28 +1012,28 @@
         <v>-16.4557</v>
       </c>
       <c r="R4">
-        <v>0.9545</v>
+        <v>0.95450000000000002</v>
       </c>
       <c r="S4">
-        <v>0.9545</v>
+        <v>0.95450000000000002</v>
       </c>
       <c r="T4">
-        <v>0.075</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="U4">
-        <v>0.075</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="V4">
-        <v>0.0522</v>
+        <v>5.2200000000000003E-2</v>
       </c>
       <c r="W4">
-        <v>-0.1428</v>
+        <v>-0.14280000000000001</v>
       </c>
       <c r="X4">
-        <v>0.7644</v>
+        <v>0.76439999999999997</v>
       </c>
       <c r="Y4">
-        <v>-1.7172</v>
+        <v>-1.7172000000000001</v>
       </c>
       <c r="Z4">
         <v>0.2722</v>
@@ -1004,10 +1042,10 @@
         <v>0.2722</v>
       </c>
       <c r="AB4">
-        <v>0.3516</v>
+        <v>0.35160000000000002</v>
       </c>
       <c r="AC4">
-        <v>0.3516</v>
+        <v>0.35160000000000002</v>
       </c>
       <c r="AD4">
         <v>0.1191</v>
@@ -1019,13 +1057,13 @@
         <v>0.185</v>
       </c>
       <c r="AG4">
-        <v>0.0308</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="AH4">
-        <v>0.5352</v>
+        <v>0.53520000000000001</v>
       </c>
       <c r="AI4">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="AJ4">
         <v>0.2407</v>
@@ -1034,39 +1072,39 @@
         <v>0.2407</v>
       </c>
       <c r="AL4">
-        <v>0.1302</v>
+        <v>0.13020000000000001</v>
       </c>
       <c r="AM4">
-        <v>0.1302</v>
+        <v>0.13020000000000001</v>
       </c>
       <c r="AN4">
-        <v>0.2425</v>
+        <v>0.24249999999999999</v>
       </c>
       <c r="AO4">
-        <v>0.2425</v>
+        <v>0.24249999999999999</v>
       </c>
       <c r="AP4">
         <v>0.3518</v>
       </c>
       <c r="AQ4">
-        <v>0.0373</v>
+        <v>3.73E-2</v>
       </c>
       <c r="AR4">
         <v>0.2167</v>
       </c>
       <c r="AS4">
-        <v>0.0607</v>
+        <v>6.0699999999999997E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:45">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>48</v>
       </c>
       <c r="B5">
-        <v>15.841</v>
+        <v>15.840999999999999</v>
       </c>
       <c r="C5">
-        <v>47.709</v>
+        <v>47.709000000000003</v>
       </c>
       <c r="D5">
         <v>0.3</v>
@@ -1078,19 +1116,19 @@
         <v>-19.9023</v>
       </c>
       <c r="G5">
-        <v>-20.8773</v>
+        <v>-20.877300000000002</v>
       </c>
       <c r="H5">
-        <v>-0.1533</v>
+        <v>-0.15329999999999999</v>
       </c>
       <c r="I5">
-        <v>-0.1533</v>
+        <v>-0.15329999999999999</v>
       </c>
       <c r="J5">
-        <v>-0.1141</v>
+        <v>-0.11409999999999999</v>
       </c>
       <c r="K5">
-        <v>-0.1141</v>
+        <v>-0.11409999999999999</v>
       </c>
       <c r="L5">
         <v>0.1895</v>
@@ -1099,16 +1137,16 @@
         <v>-0.107</v>
       </c>
       <c r="N5">
-        <v>0.2435</v>
+        <v>0.24349999999999999</v>
       </c>
       <c r="O5">
         <v>-0.1552</v>
       </c>
       <c r="P5">
-        <v>-17.0785</v>
+        <v>-17.078499999999998</v>
       </c>
       <c r="Q5">
-        <v>-17.0785</v>
+        <v>-17.078499999999998</v>
       </c>
       <c r="R5">
         <v>-0.1487</v>
@@ -1129,52 +1167,52 @@
         <v>-0.1017</v>
       </c>
       <c r="X5">
-        <v>0.2355</v>
+        <v>0.23549999999999999</v>
       </c>
       <c r="Y5">
         <v>-0.1512</v>
       </c>
       <c r="Z5">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="AA5">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="AB5">
-        <v>0.2864</v>
+        <v>0.28639999999999999</v>
       </c>
       <c r="AC5">
-        <v>0.2864</v>
+        <v>0.28639999999999999</v>
       </c>
       <c r="AD5">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="AE5">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="AF5">
         <v>0.03</v>
       </c>
       <c r="AG5">
-        <v>0.0015</v>
+        <v>1.5E-3</v>
       </c>
       <c r="AH5">
-        <v>0.4311</v>
+        <v>0.43109999999999998</v>
       </c>
       <c r="AI5">
-        <v>0.0587</v>
+        <v>5.8700000000000002E-2</v>
       </c>
       <c r="AJ5">
-        <v>0.0112</v>
+        <v>1.12E-2</v>
       </c>
       <c r="AK5">
-        <v>0.0112</v>
+        <v>1.12E-2</v>
       </c>
       <c r="AL5">
-        <v>0.0517</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="AM5">
-        <v>0.0517</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="AN5">
         <v>0.1424</v>
@@ -1183,27 +1221,27 @@
         <v>0.1424</v>
       </c>
       <c r="AP5">
-        <v>0.1912</v>
+        <v>0.19120000000000001</v>
       </c>
       <c r="AQ5">
-        <v>0.0061</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="AR5">
-        <v>0.075</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="AS5">
-        <v>0.0092</v>
+        <v>9.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:45">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
       <c r="B6">
-        <v>15.841</v>
+        <v>15.840999999999999</v>
       </c>
       <c r="C6">
-        <v>42.109</v>
+        <v>42.109000000000002</v>
       </c>
       <c r="D6">
         <v>0.3</v>
@@ -1212,34 +1250,34 @@
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>-17.9674</v>
+        <v>-17.967400000000001</v>
       </c>
       <c r="G6">
-        <v>-18.9424</v>
+        <v>-18.942399999999999</v>
       </c>
       <c r="H6">
-        <v>-0.1161</v>
+        <v>-0.11609999999999999</v>
       </c>
       <c r="I6">
-        <v>-0.1161</v>
+        <v>-0.11609999999999999</v>
       </c>
       <c r="J6">
-        <v>-0.2256</v>
+        <v>-0.22559999999999999</v>
       </c>
       <c r="K6">
-        <v>-0.2256</v>
+        <v>-0.22559999999999999</v>
       </c>
       <c r="L6">
-        <v>0.3847</v>
+        <v>0.38469999999999999</v>
       </c>
       <c r="M6">
-        <v>-0.2018</v>
+        <v>-0.20180000000000001</v>
       </c>
       <c r="N6">
-        <v>0.1805</v>
+        <v>0.18049999999999999</v>
       </c>
       <c r="O6">
-        <v>-0.1214</v>
+        <v>-0.12139999999999999</v>
       </c>
       <c r="P6">
         <v>-15.3163</v>
@@ -1254,13 +1292,13 @@
         <v>-0.112</v>
       </c>
       <c r="T6">
-        <v>-0.2038</v>
+        <v>-0.20380000000000001</v>
       </c>
       <c r="U6">
-        <v>-0.2038</v>
+        <v>-0.20380000000000001</v>
       </c>
       <c r="V6">
-        <v>0.3472</v>
+        <v>0.34720000000000001</v>
       </c>
       <c r="W6">
         <v>-0.1827</v>
@@ -1269,78 +1307,78 @@
         <v>0.1757</v>
       </c>
       <c r="Y6">
-        <v>-0.1156</v>
+        <v>-0.11559999999999999</v>
       </c>
       <c r="Z6">
-        <v>0.0172</v>
+        <v>1.72E-2</v>
       </c>
       <c r="AA6">
-        <v>0.0172</v>
+        <v>1.72E-2</v>
       </c>
       <c r="AB6">
-        <v>0.3229</v>
+        <v>0.32290000000000002</v>
       </c>
       <c r="AC6">
-        <v>0.3229</v>
+        <v>0.32290000000000002</v>
       </c>
       <c r="AD6">
-        <v>0.0176</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="AE6">
-        <v>0.0176</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="AF6">
-        <v>0.0252</v>
+        <v>2.52E-2</v>
       </c>
       <c r="AG6">
-        <v>0.0026</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="AH6">
-        <v>0.4878</v>
+        <v>0.48780000000000001</v>
       </c>
       <c r="AI6">
-        <v>0.06809999999999999</v>
+        <v>6.8099999999999994E-2</v>
       </c>
       <c r="AJ6">
-        <v>0.08110000000000001</v>
+        <v>8.1100000000000005E-2</v>
       </c>
       <c r="AK6">
-        <v>0.08110000000000001</v>
+        <v>8.1100000000000005E-2</v>
       </c>
       <c r="AL6">
-        <v>0.0445</v>
+        <v>4.4499999999999998E-2</v>
       </c>
       <c r="AM6">
-        <v>0.0445</v>
+        <v>4.4499999999999998E-2</v>
       </c>
       <c r="AN6">
-        <v>0.1083</v>
+        <v>0.10829999999999999</v>
       </c>
       <c r="AO6">
-        <v>0.1083</v>
+        <v>0.10829999999999999</v>
       </c>
       <c r="AP6">
-        <v>0.1622</v>
+        <v>0.16220000000000001</v>
       </c>
       <c r="AQ6">
-        <v>0.0216</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="AR6">
-        <v>0.06279999999999999</v>
+        <v>6.2799999999999995E-2</v>
       </c>
       <c r="AS6">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:45">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
       <c r="B7">
-        <v>15.841</v>
+        <v>15.840999999999999</v>
       </c>
       <c r="C7">
-        <v>37.109</v>
+        <v>37.109000000000002</v>
       </c>
       <c r="D7">
         <v>0.3</v>
@@ -1349,28 +1387,28 @@
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>-17.5476</v>
+        <v>-17.547599999999999</v>
       </c>
       <c r="G7">
-        <v>-18.5226</v>
+        <v>-18.522600000000001</v>
       </c>
       <c r="H7">
-        <v>-0.2042</v>
+        <v>-0.20419999999999999</v>
       </c>
       <c r="I7">
-        <v>-0.2042</v>
+        <v>-0.20419999999999999</v>
       </c>
       <c r="J7">
-        <v>0.1501</v>
+        <v>0.15010000000000001</v>
       </c>
       <c r="K7">
-        <v>0.1501</v>
+        <v>0.15010000000000001</v>
       </c>
       <c r="L7">
-        <v>0.1175</v>
+        <v>0.11749999999999999</v>
       </c>
       <c r="M7">
-        <v>-0.2726</v>
+        <v>-0.27260000000000001</v>
       </c>
       <c r="N7">
         <v>0.3402</v>
@@ -1379,10 +1417,10 @@
         <v>-0.1908</v>
       </c>
       <c r="P7">
-        <v>-14.7868</v>
+        <v>-14.786799999999999</v>
       </c>
       <c r="Q7">
-        <v>-14.7868</v>
+        <v>-14.786799999999999</v>
       </c>
       <c r="R7">
         <v>-0.1588</v>
@@ -1391,28 +1429,28 @@
         <v>-0.1588</v>
       </c>
       <c r="T7">
-        <v>0.09859999999999999</v>
+        <v>9.8599999999999993E-2</v>
       </c>
       <c r="U7">
-        <v>0.09859999999999999</v>
+        <v>9.8599999999999993E-2</v>
       </c>
       <c r="V7">
-        <v>0.0743</v>
+        <v>7.4300000000000005E-2</v>
       </c>
       <c r="W7">
         <v>-0.182</v>
       </c>
       <c r="X7">
-        <v>0.2638</v>
+        <v>0.26379999999999998</v>
       </c>
       <c r="Y7">
-        <v>-0.149</v>
+        <v>-0.14899999999999999</v>
       </c>
       <c r="Z7">
-        <v>0.07389999999999999</v>
+        <v>7.3899999999999993E-2</v>
       </c>
       <c r="AA7">
-        <v>0.07389999999999999</v>
+        <v>7.3899999999999993E-2</v>
       </c>
       <c r="AB7">
         <v>0.3654</v>
@@ -1421,63 +1459,63 @@
         <v>0.3654</v>
       </c>
       <c r="AD7">
-        <v>0.0308</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="AE7">
-        <v>0.0308</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="AF7">
-        <v>0.0452</v>
+        <v>4.5199999999999997E-2</v>
       </c>
       <c r="AG7">
-        <v>0.0078</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="AH7">
-        <v>0.547</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="AI7">
-        <v>0.0723</v>
+        <v>7.2300000000000003E-2</v>
       </c>
       <c r="AJ7">
-        <v>0.4727</v>
+        <v>0.47270000000000001</v>
       </c>
       <c r="AK7">
-        <v>0.4727</v>
+        <v>0.47270000000000001</v>
       </c>
       <c r="AL7">
-        <v>0.0433</v>
+        <v>4.3299999999999998E-2</v>
       </c>
       <c r="AM7">
-        <v>0.0433</v>
+        <v>4.3299999999999998E-2</v>
       </c>
       <c r="AN7">
-        <v>0.2562</v>
+        <v>0.25619999999999998</v>
       </c>
       <c r="AO7">
-        <v>0.2562</v>
+        <v>0.25619999999999998</v>
       </c>
       <c r="AP7">
-        <v>0.3786</v>
+        <v>0.37859999999999999</v>
       </c>
       <c r="AQ7">
-        <v>0.046</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="AR7">
-        <v>0.0599</v>
+        <v>5.9900000000000002E-2</v>
       </c>
       <c r="AS7">
-        <v>0.0067</v>
+        <v>6.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:45">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8">
-        <v>22.249</v>
+        <v>22.248999999999999</v>
       </c>
       <c r="C8">
-        <v>47.709</v>
+        <v>47.709000000000003</v>
       </c>
       <c r="D8">
         <v>0.3</v>
@@ -1489,37 +1527,37 @@
         <v>-24.6799</v>
       </c>
       <c r="G8">
-        <v>-25.6549</v>
+        <v>-25.654900000000001</v>
       </c>
       <c r="H8">
-        <v>-2.162</v>
+        <v>-2.1619999999999999</v>
       </c>
       <c r="I8">
-        <v>-2.162</v>
+        <v>-2.1619999999999999</v>
       </c>
       <c r="J8">
-        <v>0.0286</v>
+        <v>2.86E-2</v>
       </c>
       <c r="K8">
-        <v>0.0286</v>
+        <v>2.86E-2</v>
       </c>
       <c r="L8">
-        <v>0.0156</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="M8">
-        <v>-0.0588</v>
+        <v>-5.8799999999999998E-2</v>
       </c>
       <c r="N8">
-        <v>3.8179</v>
+        <v>3.8178999999999998</v>
       </c>
       <c r="O8">
-        <v>-1.8033</v>
+        <v>-1.8032999999999999</v>
       </c>
       <c r="P8">
-        <v>-21.5542</v>
+        <v>-21.554200000000002</v>
       </c>
       <c r="Q8">
-        <v>-21.5542</v>
+        <v>-21.554200000000002</v>
       </c>
       <c r="R8">
         <v>-2.0221</v>
@@ -1528,64 +1566,64 @@
         <v>-2.0221</v>
       </c>
       <c r="T8">
-        <v>0.0289</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="U8">
-        <v>0.0289</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="V8">
-        <v>0.0173</v>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="W8">
-        <v>-0.0577</v>
+        <v>-5.7700000000000001E-2</v>
       </c>
       <c r="X8">
-        <v>3.5692</v>
+        <v>3.5691999999999999</v>
       </c>
       <c r="Y8">
-        <v>-1.6884</v>
+        <v>-1.6883999999999999</v>
       </c>
       <c r="Z8">
-        <v>0.0353</v>
+        <v>3.5299999999999998E-2</v>
       </c>
       <c r="AA8">
-        <v>0.0353</v>
+        <v>3.5299999999999998E-2</v>
       </c>
       <c r="AB8">
-        <v>0.2834</v>
+        <v>0.28339999999999999</v>
       </c>
       <c r="AC8">
-        <v>0.2834</v>
+        <v>0.28339999999999999</v>
       </c>
       <c r="AD8">
-        <v>0.026</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="AE8">
-        <v>0.026</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="AF8">
         <v>0.04</v>
       </c>
       <c r="AG8">
-        <v>0.0065</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="AH8">
-        <v>0.4286</v>
+        <v>0.42859999999999998</v>
       </c>
       <c r="AI8">
-        <v>0.0602</v>
+        <v>6.0199999999999997E-2</v>
       </c>
       <c r="AJ8">
-        <v>0.0394</v>
+        <v>3.9399999999999998E-2</v>
       </c>
       <c r="AK8">
-        <v>0.0394</v>
+        <v>3.9399999999999998E-2</v>
       </c>
       <c r="AL8">
-        <v>0.0534</v>
+        <v>5.3400000000000003E-2</v>
       </c>
       <c r="AM8">
-        <v>0.0534</v>
+        <v>5.3400000000000003E-2</v>
       </c>
       <c r="AN8">
         <v>0.1371</v>
@@ -1594,27 +1632,27 @@
         <v>0.1371</v>
       </c>
       <c r="AP8">
-        <v>0.1834</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="AQ8">
-        <v>0.0062</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="AR8">
-        <v>0.0756</v>
+        <v>7.5600000000000001E-2</v>
       </c>
       <c r="AS8">
-        <v>0.0123</v>
+        <v>1.23E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:45">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9">
-        <v>22.249</v>
+        <v>22.248999999999999</v>
       </c>
       <c r="C9">
-        <v>42.109</v>
+        <v>42.109000000000002</v>
       </c>
       <c r="D9">
         <v>0.3</v>
@@ -1623,94 +1661,94 @@
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>-24.046</v>
+        <v>-24.045999999999999</v>
       </c>
       <c r="G9">
-        <v>-25.021</v>
+        <v>-25.021000000000001</v>
       </c>
       <c r="H9">
-        <v>-2.7568</v>
+        <v>-2.7568000000000001</v>
       </c>
       <c r="I9">
-        <v>-2.7568</v>
+        <v>-2.7568000000000001</v>
       </c>
       <c r="J9">
-        <v>-0.2701</v>
+        <v>-0.27010000000000001</v>
       </c>
       <c r="K9">
-        <v>-0.2701</v>
+        <v>-0.27010000000000001</v>
       </c>
       <c r="L9">
-        <v>0.464</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="M9">
-        <v>-0.2383</v>
+        <v>-0.23830000000000001</v>
       </c>
       <c r="N9">
-        <v>4.8796</v>
+        <v>4.8795999999999999</v>
       </c>
       <c r="O9">
         <v>-2.2881</v>
       </c>
       <c r="P9">
-        <v>-20.9852</v>
+        <v>-20.985199999999999</v>
       </c>
       <c r="Q9">
-        <v>-20.9852</v>
+        <v>-20.985199999999999</v>
       </c>
       <c r="R9">
-        <v>-2.5676</v>
+        <v>-2.5676000000000001</v>
       </c>
       <c r="S9">
-        <v>-2.5676</v>
+        <v>-2.5676000000000001</v>
       </c>
       <c r="T9">
-        <v>-0.2481</v>
+        <v>-0.24809999999999999</v>
       </c>
       <c r="U9">
-        <v>-0.2481</v>
+        <v>-0.24809999999999999</v>
       </c>
       <c r="V9">
-        <v>0.427</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="W9">
-        <v>-0.2181</v>
+        <v>-0.21809999999999999</v>
       </c>
       <c r="X9">
-        <v>4.5453</v>
+        <v>4.5453000000000001</v>
       </c>
       <c r="Y9">
-        <v>-2.1304</v>
+        <v>-2.1303999999999998</v>
       </c>
       <c r="Z9">
-        <v>0.0585</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="AA9">
-        <v>0.0585</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="AB9">
-        <v>0.3114</v>
+        <v>0.31140000000000001</v>
       </c>
       <c r="AC9">
-        <v>0.3114</v>
+        <v>0.31140000000000001</v>
       </c>
       <c r="AD9">
-        <v>0.0108</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="AE9">
-        <v>0.0108</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="AF9">
-        <v>0.0182</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="AG9">
-        <v>0.0076</v>
+        <v>7.6E-3</v>
       </c>
       <c r="AH9">
-        <v>0.4784</v>
+        <v>0.47839999999999999</v>
       </c>
       <c r="AI9">
-        <v>0.0736</v>
+        <v>7.3599999999999999E-2</v>
       </c>
       <c r="AJ9">
         <v>0.15</v>
@@ -1719,39 +1757,39 @@
         <v>0.15</v>
       </c>
       <c r="AL9">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="AM9">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="AN9">
-        <v>0.1029</v>
+        <v>0.10290000000000001</v>
       </c>
       <c r="AO9">
-        <v>0.1029</v>
+        <v>0.10290000000000001</v>
       </c>
       <c r="AP9">
-        <v>0.1543</v>
+        <v>0.15429999999999999</v>
       </c>
       <c r="AQ9">
-        <v>0.0221</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="AR9">
-        <v>0.0592</v>
+        <v>5.9200000000000003E-2</v>
       </c>
       <c r="AS9">
-        <v>0.0108</v>
+        <v>1.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:45">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>53</v>
       </c>
       <c r="B10">
-        <v>22.249</v>
+        <v>22.248999999999999</v>
       </c>
       <c r="C10">
-        <v>37.109</v>
+        <v>37.109000000000002</v>
       </c>
       <c r="D10">
         <v>0.3</v>
@@ -1760,124 +1798,124 @@
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>-23.2344</v>
+        <v>-23.234400000000001</v>
       </c>
       <c r="G10">
-        <v>-24.2094</v>
+        <v>-24.209399999999999</v>
       </c>
       <c r="H10">
-        <v>-2.691</v>
+        <v>-2.6909999999999998</v>
       </c>
       <c r="I10">
-        <v>-2.691</v>
+        <v>-2.6909999999999998</v>
       </c>
       <c r="J10">
-        <v>0.1238</v>
+        <v>0.12379999999999999</v>
       </c>
       <c r="K10">
-        <v>0.1238</v>
+        <v>0.12379999999999999</v>
       </c>
       <c r="L10">
-        <v>0.09660000000000001</v>
+        <v>9.6600000000000005E-2</v>
       </c>
       <c r="M10">
-        <v>-0.2254</v>
+        <v>-0.22539999999999999</v>
       </c>
       <c r="N10">
-        <v>4.7653</v>
+        <v>4.7652999999999999</v>
       </c>
       <c r="O10">
-        <v>-2.2312</v>
+        <v>-2.2311999999999999</v>
       </c>
       <c r="P10">
-        <v>-20.0814</v>
+        <v>-20.081399999999999</v>
       </c>
       <c r="Q10">
-        <v>-20.0814</v>
+        <v>-20.081399999999999</v>
       </c>
       <c r="R10">
-        <v>-2.5193</v>
+        <v>-2.5192999999999999</v>
       </c>
       <c r="S10">
-        <v>-2.5193</v>
+        <v>-2.5192999999999999</v>
       </c>
       <c r="T10">
-        <v>0.09039999999999999</v>
+        <v>9.0399999999999994E-2</v>
       </c>
       <c r="U10">
-        <v>0.09039999999999999</v>
+        <v>9.0399999999999994E-2</v>
       </c>
       <c r="V10">
-        <v>0.0696</v>
+        <v>6.9599999999999995E-2</v>
       </c>
       <c r="W10">
         <v>-0.1653</v>
       </c>
       <c r="X10">
-        <v>4.4643</v>
+        <v>4.4642999999999997</v>
       </c>
       <c r="Y10">
-        <v>-2.0858</v>
+        <v>-2.0857999999999999</v>
       </c>
       <c r="Z10">
-        <v>0.3143</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="AA10">
-        <v>0.3143</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="AB10">
-        <v>0.3309</v>
+        <v>0.33090000000000003</v>
       </c>
       <c r="AC10">
-        <v>0.3309</v>
+        <v>0.33090000000000003</v>
       </c>
       <c r="AD10">
-        <v>0.0866</v>
+        <v>8.6599999999999996E-2</v>
       </c>
       <c r="AE10">
-        <v>0.0866</v>
+        <v>8.6599999999999996E-2</v>
       </c>
       <c r="AF10">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="AG10">
-        <v>0.0337</v>
+        <v>3.3700000000000001E-2</v>
       </c>
       <c r="AH10">
-        <v>0.5188</v>
+        <v>0.51880000000000004</v>
       </c>
       <c r="AI10">
-        <v>0.0886</v>
+        <v>8.8599999999999998E-2</v>
       </c>
       <c r="AJ10">
-        <v>0.5627</v>
+        <v>0.56269999999999998</v>
       </c>
       <c r="AK10">
-        <v>0.5627</v>
+        <v>0.56269999999999998</v>
       </c>
       <c r="AL10">
-        <v>0.0321</v>
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="AM10">
-        <v>0.0321</v>
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="AN10">
-        <v>0.2731</v>
+        <v>0.27310000000000001</v>
       </c>
       <c r="AO10">
-        <v>0.2731</v>
+        <v>0.27310000000000001</v>
       </c>
       <c r="AP10">
-        <v>0.4109</v>
+        <v>0.41089999999999999</v>
       </c>
       <c r="AQ10">
-        <v>0.0565</v>
+        <v>5.6500000000000002E-2</v>
       </c>
       <c r="AR10">
-        <v>0.0512</v>
+        <v>5.1200000000000002E-2</v>
       </c>
       <c r="AS10">
-        <v>0.0095</v>
+        <v>9.4999999999999998E-3</v>
       </c>
     </row>
   </sheetData>
